--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -2289,45 +2289,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107342</v>
+        <v>130107311</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507376</v>
+        <v>507355</v>
       </c>
       <c r="R16" t="n">
-        <v>7032813</v>
+        <v>7032851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,19 +2366,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2391,49 +2396,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107311</v>
+        <v>130107342</v>
       </c>
       <c r="B17" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507355</v>
+        <v>507376</v>
       </c>
       <c r="R17" t="n">
-        <v>7032851</v>
+        <v>7032813</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,20 +2469,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2501,7 +2501,7 @@
         <v>130107312</v>
       </c>
       <c r="B18" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>130107313</v>
       </c>
       <c r="B25" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107321</v>
       </c>
       <c r="B2" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130107322</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>130107354</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>130107341</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>130107304</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107323</v>
+        <v>130107353</v>
       </c>
       <c r="B7" t="n">
-        <v>80200</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,37 +1287,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507416</v>
+        <v>507521</v>
       </c>
       <c r="R7" t="n">
-        <v>7032925</v>
+        <v>7032767</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,34 +1360,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1407,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107353</v>
+        <v>130107323</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>80285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,34 +1389,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507521</v>
+        <v>507416</v>
       </c>
       <c r="R8" t="n">
-        <v>7032767</v>
+        <v>7032925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1456,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,8 +1465,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1512,7 +1512,7 @@
         <v>130107345</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>130107355</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>130107356</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>130107326</v>
       </c>
       <c r="B12" t="n">
-        <v>80236</v>
+        <v>80321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>130107350</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130107305</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>130107343</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2289,49 +2289,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107311</v>
+        <v>130107342</v>
       </c>
       <c r="B16" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507355</v>
+        <v>507376</v>
       </c>
       <c r="R16" t="n">
-        <v>7032851</v>
+        <v>7032813</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,20 +2362,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2396,45 +2391,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107342</v>
+        <v>130107311</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507376</v>
+        <v>507355</v>
       </c>
       <c r="R17" t="n">
-        <v>7032813</v>
+        <v>7032851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,19 +2468,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2501,7 +2501,7 @@
         <v>130107312</v>
       </c>
       <c r="B18" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>130107352</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>130107303</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130107344</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>130107351</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107346</v>
+        <v>130107348</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507521</v>
+        <v>507432</v>
       </c>
       <c r="R23" t="n">
-        <v>7032862</v>
+        <v>7032888</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gammal gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,45 +3177,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107348</v>
+        <v>130107313</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507432</v>
+        <v>507399</v>
       </c>
       <c r="R24" t="n">
-        <v>7032888</v>
+        <v>7032831</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,19 +3254,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3279,49 +3284,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107313</v>
+        <v>130107346</v>
       </c>
       <c r="B25" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507399</v>
+        <v>507521</v>
       </c>
       <c r="R25" t="n">
-        <v>7032831</v>
+        <v>7032862</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3356,20 +3357,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3386,10 +3386,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107349</v>
+        <v>130107347</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507397</v>
+        <v>507473</v>
       </c>
       <c r="R26" t="n">
-        <v>7032912</v>
+        <v>7032872</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107347</v>
+        <v>130107349</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507473</v>
+        <v>507397</v>
       </c>
       <c r="R27" t="n">
-        <v>7032872</v>
+        <v>7032912</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107322</v>
+        <v>130107341</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507355</v>
+        <v>507330</v>
       </c>
       <c r="R3" t="n">
-        <v>7032906</v>
+        <v>7032840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,34 +890,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -937,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107354</v>
+        <v>130107322</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,34 +919,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507440</v>
+        <v>507355</v>
       </c>
       <c r="R4" t="n">
-        <v>7032815</v>
+        <v>7032906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,8 +995,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107341</v>
+        <v>130107354</v>
       </c>
       <c r="B5" t="n">
         <v>79180</v>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507330</v>
+        <v>507440</v>
       </c>
       <c r="R5" t="n">
-        <v>7032840</v>
+        <v>7032815</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107353</v>
+        <v>130107323</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,34 +1287,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507521</v>
+        <v>507416</v>
       </c>
       <c r="R7" t="n">
-        <v>7032767</v>
+        <v>7032925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1354,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,8 +1363,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1378,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107323</v>
+        <v>130107345</v>
       </c>
       <c r="B8" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,37 +1418,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507416</v>
+        <v>507468</v>
       </c>
       <c r="R8" t="n">
-        <v>7032925</v>
+        <v>7032839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1482,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,34 +1491,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1509,7 +1509,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107345</v>
+        <v>130107353</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507468</v>
+        <v>507521</v>
       </c>
       <c r="R9" t="n">
-        <v>7032839</v>
+        <v>7032767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107350</v>
+        <v>130107305</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,34 +1961,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507429</v>
+        <v>507427</v>
       </c>
       <c r="R13" t="n">
-        <v>7032901</v>
+        <v>7032906</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2033,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,6 +2044,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2052,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107305</v>
+        <v>130107350</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,42 +2096,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507427</v>
+        <v>507429</v>
       </c>
       <c r="R14" t="n">
-        <v>7032906</v>
+        <v>7032901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2160,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,31 +2171,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107341</v>
+        <v>130107322</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,34 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507330</v>
+        <v>507355</v>
       </c>
       <c r="R3" t="n">
-        <v>7032840</v>
+        <v>7032906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,8 +893,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107322</v>
+        <v>130107354</v>
       </c>
       <c r="B4" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,37 +948,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507355</v>
+        <v>507440</v>
       </c>
       <c r="R4" t="n">
-        <v>7032906</v>
+        <v>7032815</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,34 +1021,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107354</v>
+        <v>130107341</v>
       </c>
       <c r="B5" t="n">
         <v>79180</v>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507440</v>
+        <v>507330</v>
       </c>
       <c r="R5" t="n">
-        <v>7032815</v>
+        <v>7032840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107323</v>
+        <v>130107353</v>
       </c>
       <c r="B7" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,37 +1287,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507416</v>
+        <v>507521</v>
       </c>
       <c r="R7" t="n">
-        <v>7032925</v>
+        <v>7032767</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,34 +1360,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1407,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107345</v>
+        <v>130107323</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,34 +1389,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507468</v>
+        <v>507416</v>
       </c>
       <c r="R8" t="n">
-        <v>7032839</v>
+        <v>7032925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1456,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,8 +1465,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1509,7 +1509,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107353</v>
+        <v>130107345</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507521</v>
+        <v>507468</v>
       </c>
       <c r="R9" t="n">
-        <v>7032767</v>
+        <v>7032839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3075,45 +3075,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107348</v>
+        <v>130107313</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507432</v>
+        <v>507399</v>
       </c>
       <c r="R23" t="n">
-        <v>7032888</v>
+        <v>7032831</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,19 +3152,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3177,49 +3182,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107313</v>
+        <v>130107346</v>
       </c>
       <c r="B24" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507399</v>
+        <v>507521</v>
       </c>
       <c r="R24" t="n">
-        <v>7032831</v>
+        <v>7032862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,20 +3255,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3284,7 +3284,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107346</v>
+        <v>130107348</v>
       </c>
       <c r="B25" t="n">
         <v>79180</v>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507521</v>
+        <v>507432</v>
       </c>
       <c r="R25" t="n">
-        <v>7032862</v>
+        <v>7032888</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gammal gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107353</v>
+        <v>130107323</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,34 +1287,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507521</v>
+        <v>507416</v>
       </c>
       <c r="R7" t="n">
-        <v>7032767</v>
+        <v>7032925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1354,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,8 +1363,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1378,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107323</v>
+        <v>130107353</v>
       </c>
       <c r="B8" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,37 +1418,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507416</v>
+        <v>507521</v>
       </c>
       <c r="R8" t="n">
-        <v>7032925</v>
+        <v>7032767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1482,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,34 +1491,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2289,45 +2289,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107342</v>
+        <v>130107311</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507376</v>
+        <v>507355</v>
       </c>
       <c r="R16" t="n">
-        <v>7032813</v>
+        <v>7032851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,19 +2366,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2391,49 +2396,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107311</v>
+        <v>130107342</v>
       </c>
       <c r="B17" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507355</v>
+        <v>507376</v>
       </c>
       <c r="R17" t="n">
-        <v>7032851</v>
+        <v>7032813</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,20 +2469,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -3386,7 +3386,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107347</v>
+        <v>130107349</v>
       </c>
       <c r="B26" t="n">
         <v>79180</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507473</v>
+        <v>507397</v>
       </c>
       <c r="R26" t="n">
-        <v>7032872</v>
+        <v>7032912</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107349</v>
+        <v>130107347</v>
       </c>
       <c r="B27" t="n">
         <v>79180</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507397</v>
+        <v>507473</v>
       </c>
       <c r="R27" t="n">
-        <v>7032912</v>
+        <v>7032872</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107322</v>
+        <v>130107354</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507355</v>
+        <v>507440</v>
       </c>
       <c r="R3" t="n">
-        <v>7032906</v>
+        <v>7032815</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,34 +890,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -937,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107354</v>
+        <v>130107341</v>
       </c>
       <c r="B4" t="n">
         <v>79180</v>
@@ -972,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507440</v>
+        <v>507330</v>
       </c>
       <c r="R4" t="n">
-        <v>7032815</v>
+        <v>7032840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1039,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107341</v>
+        <v>130107322</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,34 +1021,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507330</v>
+        <v>507355</v>
       </c>
       <c r="R5" t="n">
-        <v>7032840</v>
+        <v>7032906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,8 +1097,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107323</v>
+        <v>130107353</v>
       </c>
       <c r="B7" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,37 +1287,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507416</v>
+        <v>507521</v>
       </c>
       <c r="R7" t="n">
-        <v>7032925</v>
+        <v>7032767</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,34 +1360,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1407,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107353</v>
+        <v>130107345</v>
       </c>
       <c r="B8" t="n">
         <v>79180</v>
@@ -1442,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507521</v>
+        <v>507468</v>
       </c>
       <c r="R8" t="n">
-        <v>7032767</v>
+        <v>7032839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1509,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107345</v>
+        <v>130107323</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,34 +1491,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507468</v>
+        <v>507416</v>
       </c>
       <c r="R9" t="n">
-        <v>7032839</v>
+        <v>7032925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1558,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,8 +1567,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1611,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107355</v>
+        <v>130107356</v>
       </c>
       <c r="B10" t="n">
         <v>79180</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507422</v>
+        <v>507326</v>
       </c>
       <c r="R10" t="n">
-        <v>7032836</v>
+        <v>7032797</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107356</v>
+        <v>130107355</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507326</v>
+        <v>507422</v>
       </c>
       <c r="R11" t="n">
-        <v>7032797</v>
+        <v>7032836</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107305</v>
+        <v>130107350</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,42 +1961,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507427</v>
+        <v>507429</v>
       </c>
       <c r="R13" t="n">
-        <v>7032906</v>
+        <v>7032901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2025,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,31 +2036,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2085,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107350</v>
+        <v>130107305</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,34 +2063,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507429</v>
+        <v>507427</v>
       </c>
       <c r="R14" t="n">
-        <v>7032901</v>
+        <v>7032906</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2135,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,6 +2146,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2289,49 +2289,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107311</v>
+        <v>130107342</v>
       </c>
       <c r="B16" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507355</v>
+        <v>507376</v>
       </c>
       <c r="R16" t="n">
-        <v>7032851</v>
+        <v>7032813</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,20 +2362,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2396,45 +2391,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107342</v>
+        <v>130107311</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507376</v>
+        <v>507355</v>
       </c>
       <c r="R17" t="n">
-        <v>7032813</v>
+        <v>7032851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,19 +2468,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -3075,49 +3075,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107313</v>
+        <v>130107348</v>
       </c>
       <c r="B23" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507399</v>
+        <v>507432</v>
       </c>
       <c r="R23" t="n">
-        <v>7032831</v>
+        <v>7032888</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3152,20 +3148,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3284,45 +3279,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107348</v>
+        <v>130107313</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507432</v>
+        <v>507399</v>
       </c>
       <c r="R25" t="n">
-        <v>7032888</v>
+        <v>7032831</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3357,19 +3356,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3386,7 +3386,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107349</v>
+        <v>130107347</v>
       </c>
       <c r="B26" t="n">
         <v>79180</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507397</v>
+        <v>507473</v>
       </c>
       <c r="R26" t="n">
-        <v>7032912</v>
+        <v>7032872</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107347</v>
+        <v>130107349</v>
       </c>
       <c r="B27" t="n">
         <v>79180</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507473</v>
+        <v>507397</v>
       </c>
       <c r="R27" t="n">
-        <v>7032872</v>
+        <v>7032912</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107354</v>
+        <v>130107322</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,34 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507440</v>
+        <v>507355</v>
       </c>
       <c r="R3" t="n">
-        <v>7032815</v>
+        <v>7032906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,8 +893,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107341</v>
+        <v>130107354</v>
       </c>
       <c r="B4" t="n">
         <v>79180</v>
@@ -943,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507330</v>
+        <v>507440</v>
       </c>
       <c r="R4" t="n">
-        <v>7032840</v>
+        <v>7032815</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107322</v>
+        <v>130107341</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,37 +1050,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507355</v>
+        <v>507330</v>
       </c>
       <c r="R5" t="n">
-        <v>7032906</v>
+        <v>7032840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1114,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,34 +1123,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107353</v>
+        <v>130107323</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,34 +1287,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507521</v>
+        <v>507416</v>
       </c>
       <c r="R7" t="n">
-        <v>7032767</v>
+        <v>7032925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1354,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,8 +1363,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1378,7 +1407,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107345</v>
+        <v>130107353</v>
       </c>
       <c r="B8" t="n">
         <v>79180</v>
@@ -1413,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507468</v>
+        <v>507521</v>
       </c>
       <c r="R8" t="n">
-        <v>7032839</v>
+        <v>7032767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107323</v>
+        <v>130107345</v>
       </c>
       <c r="B9" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,37 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507416</v>
+        <v>507468</v>
       </c>
       <c r="R9" t="n">
-        <v>7032925</v>
+        <v>7032839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1584,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,34 +1593,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1611,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107356</v>
+        <v>130107355</v>
       </c>
       <c r="B10" t="n">
         <v>79180</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507326</v>
+        <v>507422</v>
       </c>
       <c r="R10" t="n">
-        <v>7032797</v>
+        <v>7032836</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107355</v>
+        <v>130107356</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507422</v>
+        <v>507326</v>
       </c>
       <c r="R11" t="n">
-        <v>7032836</v>
+        <v>7032797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107350</v>
+        <v>130107305</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,34 +1961,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507429</v>
+        <v>507427</v>
       </c>
       <c r="R13" t="n">
-        <v>7032901</v>
+        <v>7032906</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2033,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,6 +2044,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2052,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107305</v>
+        <v>130107350</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,42 +2096,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507427</v>
+        <v>507429</v>
       </c>
       <c r="R14" t="n">
-        <v>7032906</v>
+        <v>7032901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2160,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,31 +2171,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -3075,7 +3075,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107348</v>
+        <v>130107346</v>
       </c>
       <c r="B23" t="n">
         <v>79180</v>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507432</v>
+        <v>507521</v>
       </c>
       <c r="R23" t="n">
-        <v>7032888</v>
+        <v>7032862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,7 +3177,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107346</v>
+        <v>130107348</v>
       </c>
       <c r="B24" t="n">
         <v>79180</v>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507521</v>
+        <v>507432</v>
       </c>
       <c r="R24" t="n">
-        <v>7032862</v>
+        <v>7032888</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gammal gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3386,7 +3386,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107347</v>
+        <v>130107349</v>
       </c>
       <c r="B26" t="n">
         <v>79180</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507473</v>
+        <v>507397</v>
       </c>
       <c r="R26" t="n">
-        <v>7032872</v>
+        <v>7032912</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107349</v>
+        <v>130107347</v>
       </c>
       <c r="B27" t="n">
         <v>79180</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507397</v>
+        <v>507473</v>
       </c>
       <c r="R27" t="n">
-        <v>7032912</v>
+        <v>7032872</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107350</v>
+        <v>130107305</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,34 +1961,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507429</v>
+        <v>507427</v>
       </c>
       <c r="R13" t="n">
-        <v>7032901</v>
+        <v>7032906</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2033,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,6 +2044,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2052,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107305</v>
+        <v>130107350</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,42 +2096,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507427</v>
+        <v>507429</v>
       </c>
       <c r="R14" t="n">
-        <v>7032906</v>
+        <v>7032901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2160,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,31 +2171,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107305</v>
+        <v>130107350</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,42 +1961,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507427</v>
+        <v>507429</v>
       </c>
       <c r="R13" t="n">
-        <v>7032906</v>
+        <v>7032901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2025,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,31 +2036,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2085,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107350</v>
+        <v>130107305</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,34 +2063,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507429</v>
+        <v>507427</v>
       </c>
       <c r="R14" t="n">
-        <v>7032901</v>
+        <v>7032906</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2135,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,6 +2146,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107321</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130107354</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>130107341</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130107322</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107353</v>
+        <v>130107323</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,34 +1287,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507521</v>
+        <v>507416</v>
       </c>
       <c r="R7" t="n">
-        <v>7032767</v>
+        <v>7032925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1354,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,8 +1363,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1378,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107345</v>
+        <v>130107353</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507468</v>
+        <v>507521</v>
       </c>
       <c r="R8" t="n">
-        <v>7032839</v>
+        <v>7032767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107323</v>
+        <v>130107345</v>
       </c>
       <c r="B9" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,37 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507416</v>
+        <v>507468</v>
       </c>
       <c r="R9" t="n">
-        <v>7032925</v>
+        <v>7032839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1584,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,34 +1593,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1614,7 +1614,7 @@
         <v>130107355</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>130107356</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>130107326</v>
       </c>
       <c r="B12" t="n">
-        <v>80321</v>
+        <v>80324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107305</v>
+        <v>130107350</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,42 +1961,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507427</v>
+        <v>507429</v>
       </c>
       <c r="R13" t="n">
-        <v>7032906</v>
+        <v>7032901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2025,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,31 +2036,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2085,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107350</v>
+        <v>130107305</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,34 +2063,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507429</v>
+        <v>507427</v>
       </c>
       <c r="R14" t="n">
-        <v>7032901</v>
+        <v>7032906</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2135,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,6 +2146,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2190,7 +2190,7 @@
         <v>130107343</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>130107342</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>130107311</v>
       </c>
       <c r="B17" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>130107312</v>
       </c>
       <c r="B18" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>130107352</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130107344</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>130107351</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3075,45 +3075,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107346</v>
+        <v>130107313</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>97794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507521</v>
+        <v>507399</v>
       </c>
       <c r="R23" t="n">
-        <v>7032862</v>
+        <v>7032831</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,19 +3152,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3177,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107348</v>
+        <v>130107346</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3212,10 +3217,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507432</v>
+        <v>507521</v>
       </c>
       <c r="R24" t="n">
-        <v>7032888</v>
+        <v>7032862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3252,7 +3257,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3279,49 +3284,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107313</v>
+        <v>130107348</v>
       </c>
       <c r="B25" t="n">
-        <v>97791</v>
+        <v>79183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507399</v>
+        <v>507432</v>
       </c>
       <c r="R25" t="n">
-        <v>7032831</v>
+        <v>7032888</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3356,20 +3357,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3389,7 +3389,7 @@
         <v>130107349</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>130107347</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107321</v>
+        <v>130107341</v>
       </c>
       <c r="B2" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507522</v>
+        <v>507330</v>
       </c>
       <c r="R2" t="n">
-        <v>7032834</v>
+        <v>7032840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +759,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -806,14 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107354</v>
+        <v>130107342</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -841,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507440</v>
+        <v>507376</v>
       </c>
       <c r="R3" t="n">
-        <v>7032815</v>
+        <v>7032813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,14 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107341</v>
+        <v>130107343</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -943,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507330</v>
+        <v>507356</v>
       </c>
       <c r="R4" t="n">
-        <v>7032840</v>
+        <v>7032842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107322</v>
+        <v>130107344</v>
       </c>
       <c r="B5" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507355</v>
+        <v>507358</v>
       </c>
       <c r="R5" t="n">
-        <v>7032906</v>
+        <v>7032855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1059,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,22 +1079,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1141,53 +1112,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130107304</v>
+        <v>130107345</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507441</v>
+        <v>507468</v>
       </c>
       <c r="R6" t="n">
-        <v>7032908</v>
+        <v>7032839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,31 +1198,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1276,48 +1214,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107323</v>
+        <v>130107346</v>
       </c>
       <c r="B7" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507416</v>
+        <v>507521</v>
       </c>
       <c r="R7" t="n">
-        <v>7032925</v>
+        <v>7032862</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1289,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,34 +1298,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1407,14 +1316,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107353</v>
+        <v>130107347</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1442,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507521</v>
+        <v>507473</v>
       </c>
       <c r="R8" t="n">
-        <v>7032767</v>
+        <v>7032872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1509,14 +1418,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107345</v>
+        <v>130107348</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1544,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507468</v>
+        <v>507432</v>
       </c>
       <c r="R9" t="n">
-        <v>7032839</v>
+        <v>7032888</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1493,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gammal gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,14 +1520,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107355</v>
+        <v>130107349</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1646,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507422</v>
+        <v>507397</v>
       </c>
       <c r="R10" t="n">
-        <v>7032836</v>
+        <v>7032912</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,14 +1622,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107356</v>
+        <v>130107350</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1748,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507326</v>
+        <v>507429</v>
       </c>
       <c r="R11" t="n">
-        <v>7032797</v>
+        <v>7032901</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1697,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,52 +1724,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130107326</v>
+        <v>130107351</v>
       </c>
       <c r="B12" t="n">
-        <v>80324</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507353</v>
+        <v>507466</v>
       </c>
       <c r="R12" t="n">
-        <v>7032907</v>
+        <v>7032900</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1799,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,34 +1808,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1950,14 +1826,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107350</v>
+        <v>130107352</v>
       </c>
       <c r="B13" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1985,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507429</v>
+        <v>507537</v>
       </c>
       <c r="R13" t="n">
-        <v>7032901</v>
+        <v>7032882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +1901,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på en gran med ringhack av tretåig hackspett.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,53 +1928,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107305</v>
+        <v>130107353</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507427</v>
+        <v>507521</v>
       </c>
       <c r="R14" t="n">
-        <v>7032906</v>
+        <v>7032767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,31 +2014,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2187,14 +2030,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107343</v>
+        <v>130107354</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2222,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507356</v>
+        <v>507440</v>
       </c>
       <c r="R15" t="n">
-        <v>7032842</v>
+        <v>7032815</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,7 +2105,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,14 +2132,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107342</v>
+        <v>130107355</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2324,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507376</v>
+        <v>507422</v>
       </c>
       <c r="R16" t="n">
-        <v>7032813</v>
+        <v>7032836</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,49 +2234,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107311</v>
+        <v>130107356</v>
       </c>
       <c r="B17" t="n">
-        <v>97794</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507355</v>
+        <v>507326</v>
       </c>
       <c r="R17" t="n">
-        <v>7032851</v>
+        <v>7032797</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,20 +2307,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2498,49 +2336,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130107312</v>
+        <v>130107357</v>
       </c>
       <c r="B18" t="n">
-        <v>97794</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507337</v>
+        <v>507283</v>
       </c>
       <c r="R18" t="n">
-        <v>7032943</v>
+        <v>7032795</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,20 +2409,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2605,14 +2438,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130107352</v>
+        <v>130107358</v>
       </c>
       <c r="B19" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2640,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507537</v>
+        <v>507233</v>
       </c>
       <c r="R19" t="n">
-        <v>7032882</v>
+        <v>7032821</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2707,42 +2540,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107303</v>
+        <v>130107361</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2750,10 +2578,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507345</v>
+        <v>507236</v>
       </c>
       <c r="R20" t="n">
-        <v>7032953</v>
+        <v>7032990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2618,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2799,6 +2627,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2819,12 +2648,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2842,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107344</v>
+        <v>130107321</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,21 +2682,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2880,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507358</v>
+        <v>507522</v>
       </c>
       <c r="R21" t="n">
-        <v>7032855</v>
+        <v>7032834</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2920,7 +2749,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd och 48 cm i brösthöjdsdiameter.</t>
+          <t>Lunglav på en asp med tickor (naturvärdesträd). På fyndplatsen finns fler värdefulla aspar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,22 +2769,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2973,10 +2802,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107351</v>
+        <v>130107322</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,34 +2813,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507466</v>
+        <v>507355</v>
       </c>
       <c r="R22" t="n">
-        <v>7032900</v>
+        <v>7032906</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,8 +2889,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3075,38 +2933,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107313</v>
+        <v>130107323</v>
       </c>
       <c r="B23" t="n">
-        <v>97794</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3114,10 +2971,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507399</v>
+        <v>507416</v>
       </c>
       <c r="R23" t="n">
-        <v>7032831</v>
+        <v>7032925</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3152,6 +3009,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3165,6 +3027,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3182,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107346</v>
+        <v>130107324</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,34 +3075,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507521</v>
+        <v>507238</v>
       </c>
       <c r="R24" t="n">
-        <v>7032862</v>
+        <v>7032941</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3257,7 +3146,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>I riklig mängd på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,8 +3155,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3284,45 +3199,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107348</v>
+        <v>130107326</v>
       </c>
       <c r="B25" t="n">
-        <v>79183</v>
+        <v>80468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507432</v>
+        <v>507353</v>
       </c>
       <c r="R25" t="n">
-        <v>7032888</v>
+        <v>7032907</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3359,7 +3281,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog.</t>
+          <t>På en grov gammal tvåstammig sälg med grov barkstruktur.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3368,8 +3290,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3386,45 +3334,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107349</v>
+        <v>130107327</v>
       </c>
       <c r="B26" t="n">
-        <v>79183</v>
+        <v>80468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507397</v>
+        <v>507239</v>
       </c>
       <c r="R26" t="n">
-        <v>7032912</v>
+        <v>7032943</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3461,7 +3416,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,8 +3425,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3488,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107347</v>
+        <v>130107303</v>
       </c>
       <c r="B27" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3499,34 +3475,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507473</v>
+        <v>507345</v>
       </c>
       <c r="R27" t="n">
-        <v>7032872</v>
+        <v>7032953</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3547,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3574,6 +3558,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3587,6 +3596,597 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130107304</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>507441</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7032908</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130107305</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>507427</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7032906</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal stående död gran vid en lucka.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130107311</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>507355</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7032851</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130107312</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>507337</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7032943</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130107313</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>507399</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7032831</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56499-2025 artfynd.xlsx
+++ b/artfynd/A 56499-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107341</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107342</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107343</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107344</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107345</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107346</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107347</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107348</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107349</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1721,6 +1771,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107350</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107351</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107352</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107353</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2129,6 +2199,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107354</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2231,6 +2306,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107355</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2333,6 +2413,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107356</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2435,6 +2520,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107357</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2537,6 +2627,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107358</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2668,6 +2763,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107361</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2799,6 +2899,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107321</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2930,6 +3035,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107322</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3061,6 +3171,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3196,6 +3311,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107324</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3331,6 +3451,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107326</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3461,6 +3586,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107327</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3596,6 +3726,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107303</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3731,6 +3866,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107304</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3866,6 +4006,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107305</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3973,6 +4118,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107311</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4080,6 +4230,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107312</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4187,8 +4342,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107313</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>